--- a/data/trans_bre/MCS12_SP_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R3-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,72</t>
+          <t>2,26; 10,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 19,07</t>
+          <t>9,78; 18,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 13,91</t>
+          <t>4,68; 13,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 8,52</t>
+          <t>0,64; 8,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 90,91</t>
+          <t>14,63; 85,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,81; 107,6</t>
+          <t>42,74; 106,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,56; 84,94</t>
+          <t>21,88; 81,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 47,79</t>
+          <t>2,71; 46,96</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 14,32</t>
+          <t>6,16; 14,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 12,74</t>
+          <t>4,86; 13,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,98</t>
+          <t>5,0; 12,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 21,63</t>
+          <t>8,4; 21,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,79; 80,94</t>
+          <t>26,89; 78,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 60,59</t>
+          <t>20,06; 63,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,88; 80,98</t>
+          <t>26,98; 83,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,48; 278,73</t>
+          <t>44,43; 265,71</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 13,0</t>
+          <t>4,04; 12,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 15,23</t>
+          <t>6,09; 15,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,45</t>
+          <t>3,77; 12,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 49,31</t>
+          <t>1,77; 46,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 85,49</t>
+          <t>19,79; 82,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,08; 85,22</t>
+          <t>27,54; 86,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,0; 73,9</t>
+          <t>18,06; 75,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 269,06</t>
+          <t>8,63; 246,98</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 9,94</t>
+          <t>2,33; 9,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 13,61</t>
+          <t>4,93; 13,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,26</t>
+          <t>2,35; 10,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,49</t>
+          <t>1,95; 12,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 49,74</t>
+          <t>9,61; 49,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,31; 59,26</t>
+          <t>18,41; 57,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 50,26</t>
+          <t>9,69; 50,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 69,74</t>
+          <t>10,49; 67,1</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,95</t>
+          <t>5,94; 9,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,78</t>
+          <t>8,09; 12,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,96</t>
+          <t>6,11; 10,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,09; 23,94</t>
+          <t>7,16; 25,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,56; 56,06</t>
+          <t>29,99; 56,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,85; 60,67</t>
+          <t>34,81; 59,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,23; 56,19</t>
+          <t>30,0; 55,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,82; 140,26</t>
+          <t>35,98; 160,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/MCS12_SP_R3-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R3-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 10,51</t>
+          <t>2,29; 10,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 18,95</t>
+          <t>9,41; 19,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 13,54</t>
+          <t>4,66; 13,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,42</t>
+          <t>0,22; 8,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 85,38</t>
+          <t>14,06; 82,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,74; 106,56</t>
+          <t>41,37; 108,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,88; 81,62</t>
+          <t>21,49; 82,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 46,96</t>
+          <t>1,02; 46,27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,58</t>
+          <t>10,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 14,27</t>
+          <t>6,13; 13,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 13,07</t>
+          <t>4,79; 13,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 12,28</t>
+          <t>4,83; 11,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 21,24</t>
+          <t>7,33; 13,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,89; 78,91</t>
+          <t>26,96; 77,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,06; 63,36</t>
+          <t>19,21; 62,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,98; 83,85</t>
+          <t>26,73; 81,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,43; 265,71</t>
+          <t>37,46; 88,74</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,13</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,82</t>
+          <t>3,77; 12,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 15,6</t>
+          <t>5,6; 14,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 12,42</t>
+          <t>3,6; 12,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 46,95</t>
+          <t>1,78; 10,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,79; 82,45</t>
+          <t>19,44; 86,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,54; 86,52</t>
+          <t>24,57; 82,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,06; 75,36</t>
+          <t>16,43; 74,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 246,98</t>
+          <t>7,55; 56,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,15</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,83</t>
+          <t>2,13; 10,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,2</t>
+          <t>5,42; 13,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 10,32</t>
+          <t>2,5; 10,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 12,07</t>
+          <t>5,78; 12,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 49,53</t>
+          <t>9,27; 51,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,41; 57,94</t>
+          <t>20,38; 57,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 50,48</t>
+          <t>10,49; 49,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 67,1</t>
+          <t>25,3; 69,69</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,55</t>
+          <t>8,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 9,87</t>
+          <t>5,82; 9,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,55</t>
+          <t>8,43; 12,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,13</t>
+          <t>5,87; 9,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 25,9</t>
+          <t>6,25; 10,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,99; 56,25</t>
+          <t>29,39; 56,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,81; 59,19</t>
+          <t>35,6; 59,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,0; 55,94</t>
+          <t>29,06; 54,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,98; 160,34</t>
+          <t>30,02; 54,01</t>
         </is>
       </c>
     </row>
